--- a/IOfiles/Tabulator/output/output.xlsx
+++ b/IOfiles/Tabulator/output/output.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -580,78 +580,78 @@
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>AABBA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>BBA,BAABBAAB,AABBAABB,BBAABBBA,AABBABA,BBBABA,BBBAABB</t>
+          <t>AA,BBAA,BBA,BBBA,BB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAAAA</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>BBBAAB,B,AAB,BAABBBA,BA,BB,BABA,BBAAB,BBABA,BAAB,BBA,BBAABB,AABBAAB,BAABB</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -842,30 +842,30 @@
         <v>2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="K12" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -878,30 +878,30 @@
         <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -914,13 +914,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
@@ -933,11 +933,11 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="K14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -950,98 +950,98 @@
         <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>AABBA,AA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AAB</t>
+          <t>AABA</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AABA</t>
+          <t>BBBA</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="K17" s="6" t="n">
@@ -1051,20 +1051,20 @@
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>BBAA</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
@@ -1077,57 +1077,57 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>BAAB</t>
+          <t>AABBA</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>AABBA</t>
+          <t>BBBABA</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>0</v>
@@ -1153,39 +1153,39 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BBABA</t>
+          <t>BBAABB</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K21" s="6" t="n">
@@ -1195,617 +1195,185 @@
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>BAABB</t>
+          <t>AAAAAAA</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Catalyzers as Species Information</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Reaction as product</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Condensation as products</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Cleavage as products</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Total catalyzers</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Condensation catalyzers</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Cleavage catalyzers</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Catalyzers</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Reactions as reactants</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>BBAAB</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>BBBABA</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>BBAABB</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>BBBAAB</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>AAAAAAA</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>AABBABA</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>BBBAABB</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>BAABBBA</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>AABBAAB</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>BBAABBBA</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>AABBAABB</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>BAABBAAB</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Catalyzers as Species Information</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Reaction as product</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Condensation as products</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Cleavage as products</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Total catalyzers</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Condensation catalyzers</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Cleavage catalyzers</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Catalyzers</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Reactions as reactants</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>AABBA</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>8</v>
+      <c r="K27" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B24:K24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
